--- a/Version/BATCH/ETL/APP/CDM/BIN/tran_cdm_dim_cstm_dmns_h.xlsx
+++ b/Version/BATCH/ETL/APP/CDM/BIN/tran_cdm_dim_cstm_dmns_h.xlsx
@@ -598,22 +598,22 @@
     <t>N</t>
   </si>
   <si>
+    <t>未添加企业微信</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>UNKN_</t>
   </si>
   <si>
     <t>365</t>
   </si>
   <si>
-    <t>未添加企业微信</t>
-  </si>
-  <si>
-    <t>Y</t>
+    <t>18</t>
   </si>
   <si>
     <t>1+0</t>
-  </si>
-  <si>
-    <t>18</t>
   </si>
   <si>
     <t>来源系统名</t>
@@ -11274,7 +11274,7 @@
         <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F27" t="s">
         <v>189</v>
@@ -11288,19 +11288,19 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G28" t="s">
         <v>149</v>
@@ -11317,7 +11317,7 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
         <v>188</v>
@@ -11334,19 +11334,19 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F30" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G30" t="s">
         <v>149</v>
@@ -11409,7 +11409,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
         <v>193</v>
@@ -11432,7 +11432,7 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E34" t="s">
         <v>193</v>
@@ -11455,10 +11455,10 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E35" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F35" t="s">
         <v>189</v>
@@ -11478,10 +11478,10 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F36" t="s">
         <v>189</v>
@@ -11501,10 +11501,10 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F37" t="s">
         <v>189</v>
@@ -11524,10 +11524,10 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F38" t="s">
         <v>189</v>
@@ -11547,7 +11547,7 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s">
         <v>195</v>
@@ -11570,10 +11570,10 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F40" t="s">
         <v>189</v>
@@ -11593,10 +11593,10 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F41" t="s">
         <v>189</v>
@@ -11619,7 +11619,7 @@
         <v>35</v>
       </c>
       <c r="E42" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F42" t="s">
         <v>189</v>
@@ -11639,10 +11639,10 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F43" t="s">
         <v>189</v>
@@ -11665,7 +11665,7 @@
         <v>67</v>
       </c>
       <c r="E44" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F44" t="s">
         <v>189</v>
@@ -11685,10 +11685,10 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F45" t="s">
         <v>189</v>
@@ -11708,10 +11708,10 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F46" t="s">
         <v>189</v>
@@ -11731,7 +11731,7 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
         <v>193</v>
@@ -11777,10 +11777,10 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="E49" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F49" t="s">
         <v>189</v>
@@ -11800,10 +11800,10 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F50" t="s">
         <v>189</v>
@@ -11823,10 +11823,10 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F51" t="s">
         <v>189</v>
@@ -11849,7 +11849,7 @@
         <v>43</v>
       </c>
       <c r="E52" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F52" t="s">
         <v>189</v>
@@ -11869,10 +11869,10 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="E53" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F53" t="s">
         <v>189</v>
@@ -11892,10 +11892,10 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="E54" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F54" t="s">
         <v>189</v>
@@ -11915,10 +11915,10 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E55" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F55" t="s">
         <v>189</v>
@@ -11938,10 +11938,10 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E56" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F56" t="s">
         <v>189</v>
@@ -11961,10 +11961,10 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F57" t="s">
         <v>189</v>
@@ -11987,13 +11987,13 @@
         <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F58" t="s">
         <v>182</v>
       </c>
       <c r="G58" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H58"/>
       <c r="I58"/>
@@ -12004,19 +12004,19 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E59" t="s">
         <v>185</v>
       </c>
       <c r="F59" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="H59"/>
       <c r="I59"/>
@@ -12024,13 +12024,13 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E60" t="s">
         <v>185</v>
@@ -12039,7 +12039,7 @@
         <v>182</v>
       </c>
       <c r="G60" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H60"/>
       <c r="I60"/>
@@ -12047,13 +12047,13 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D61" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E61" t="s">
         <v>185</v>
@@ -12062,7 +12062,7 @@
         <v>182</v>
       </c>
       <c r="G61" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="H61"/>
       <c r="I61"/>
@@ -12073,19 +12073,19 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F62" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G62" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="H62"/>
       <c r="I62"/>
@@ -12099,16 +12099,16 @@
         <v>113</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E63" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F63" t="s">
         <v>182</v>
       </c>
       <c r="G63" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="H63"/>
       <c r="I63"/>
@@ -12116,22 +12116,22 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D64" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F64" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G64" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="H64"/>
       <c r="I64"/>
@@ -12142,19 +12142,19 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D65" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="E65" t="s">
         <v>185</v>
       </c>
       <c r="F65" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G65" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="H65"/>
       <c r="I65"/>
@@ -12162,13 +12162,13 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E66" t="s">
         <v>185</v>
@@ -12185,13 +12185,13 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D67" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E67" t="s">
         <v>185</v>
@@ -12200,7 +12200,7 @@
         <v>182</v>
       </c>
       <c r="G67" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="H67"/>
       <c r="I67"/>
@@ -12217,13 +12217,13 @@
         <v>133</v>
       </c>
       <c r="E68" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F68" t="s">
         <v>182</v>
       </c>
       <c r="G68" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H68"/>
       <c r="I68"/>
@@ -12231,22 +12231,22 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F69" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G69" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="H69"/>
       <c r="I69"/>
@@ -12263,13 +12263,13 @@
         <v>133</v>
       </c>
       <c r="E70" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F70" t="s">
         <v>182</v>
       </c>
       <c r="G70" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="H70"/>
       <c r="I70"/>
@@ -12277,13 +12277,13 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D71" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E71" t="s">
         <v>185</v>
@@ -12292,7 +12292,7 @@
         <v>182</v>
       </c>
       <c r="G71" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="H71"/>
       <c r="I71"/>
@@ -12300,13 +12300,13 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C72" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D72" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E72" t="s">
         <v>190</v>
@@ -12315,7 +12315,7 @@
         <v>182</v>
       </c>
       <c r="G72" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="H72"/>
       <c r="I72"/>
@@ -12326,19 +12326,19 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F73" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G73" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="H73"/>
       <c r="I73"/>
@@ -12361,7 +12361,7 @@
         <v>182</v>
       </c>
       <c r="G74" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H74"/>
       <c r="I74"/>
@@ -12369,22 +12369,22 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E75" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F75" t="s">
         <v>182</v>
       </c>
       <c r="G75" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H75"/>
       <c r="I75"/>
@@ -12398,10 +12398,10 @@
         <v>11</v>
       </c>
       <c r="D76" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F76" t="s">
         <v>189</v>
@@ -12415,13 +12415,13 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D77" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E77" t="s">
         <v>190</v>
@@ -12430,7 +12430,7 @@
         <v>182</v>
       </c>
       <c r="G77" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H77"/>
       <c r="I77"/>
@@ -12438,22 +12438,22 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D78" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="E78" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F78" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G78" t="s">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="H78"/>
       <c r="I78"/>
@@ -12461,22 +12461,22 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D79" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E79" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F79" t="s">
         <v>182</v>
       </c>
       <c r="G79" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H79"/>
       <c r="I79"/>
@@ -12487,19 +12487,19 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="E80" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F80" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G80" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="H80"/>
       <c r="I80"/>
@@ -12507,22 +12507,22 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D81" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E81" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F81" t="s">
         <v>182</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="H81"/>
       <c r="I81"/>
@@ -12530,22 +12530,22 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D82" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="E82" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F82" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G82" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H82"/>
       <c r="I82"/>
@@ -12556,19 +12556,19 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D83" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="E83" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G83" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="H83"/>
       <c r="I83"/>
@@ -12576,13 +12576,13 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D84" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E84" t="s">
         <v>198</v>
@@ -12591,7 +12591,7 @@
         <v>182</v>
       </c>
       <c r="G84" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="H84"/>
       <c r="I84"/>
@@ -12605,10 +12605,10 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E85" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F85" t="s">
         <v>189</v>
@@ -12622,22 +12622,22 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="E86" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F86" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G86" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="H86"/>
       <c r="I86"/>
@@ -12651,16 +12651,16 @@
         <v>113</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F87" t="s">
         <v>182</v>
       </c>
       <c r="G87" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H87"/>
       <c r="I87"/>
@@ -12671,19 +12671,19 @@
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D88" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E88" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F88" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G88" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H88"/>
       <c r="I88"/>
@@ -12694,19 +12694,19 @@
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D89" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E89" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F89" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G89" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H89"/>
       <c r="I89"/>
@@ -12714,22 +12714,22 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C90" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D90" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E90" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F90" t="s">
         <v>182</v>
       </c>
       <c r="G90" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H90"/>
       <c r="I90"/>
@@ -12752,7 +12752,7 @@
         <v>182</v>
       </c>
       <c r="G91" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="H91"/>
       <c r="I91"/>
@@ -12763,19 +12763,19 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="E92" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F92" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G92" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H92"/>
       <c r="I92"/>
@@ -12789,16 +12789,16 @@
         <v>113</v>
       </c>
       <c r="D93" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E93" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F93" t="s">
         <v>182</v>
       </c>
       <c r="G93" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H93"/>
       <c r="I93"/>
@@ -12806,22 +12806,22 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="E94" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F94" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G94" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="H94"/>
       <c r="I94"/>
@@ -12838,13 +12838,13 @@
         <v>93</v>
       </c>
       <c r="E95" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F95" t="s">
         <v>182</v>
       </c>
       <c r="G95" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H95"/>
       <c r="I95"/>
@@ -12852,13 +12852,13 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C96" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D96" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E96" t="s">
         <v>185</v>
@@ -12875,22 +12875,22 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E97" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F97" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G97" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="H97"/>
       <c r="I97"/>

--- a/Version/BATCH/ETL/APP/CDM/BIN/tran_cdm_dim_cstm_dmns_h.xlsx
+++ b/Version/BATCH/ETL/APP/CDM/BIN/tran_cdm_dim_cstm_dmns_h.xlsx
@@ -589,22 +589,22 @@
     <t>0</t>
   </si>
   <si>
+    <t>tran_cdm_dim_cstm_dmns_h.sql</t>
+  </si>
+  <si>
     <t>s054_ecif_vwcust_f</t>
   </si>
   <si>
-    <t>tran_cdm_dim_cstm_dmns_h.sql</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>UNKN_</t>
+  </si>
+  <si>
     <t>未添加企业微信</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>UNKN_</t>
   </si>
   <si>
     <t>365</t>
@@ -11271,10 +11271,10 @@
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F27" t="s">
         <v>189</v>
@@ -11288,19 +11288,19 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="E28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F28" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G28" t="s">
         <v>149</v>
@@ -11311,19 +11311,19 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F29" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G29" t="s">
         <v>149</v>
@@ -11340,10 +11340,10 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F30" t="s">
         <v>189</v>
@@ -11363,7 +11363,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
         <v>191</v>
@@ -11386,7 +11386,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
         <v>192</v>
@@ -11455,10 +11455,10 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F35" t="s">
         <v>189</v>
@@ -11478,10 +11478,10 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F36" t="s">
         <v>189</v>
@@ -11501,10 +11501,10 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F37" t="s">
         <v>189</v>
@@ -11524,10 +11524,10 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
         <v>189</v>
@@ -11547,10 +11547,10 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F39" t="s">
         <v>189</v>
@@ -11570,10 +11570,10 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F40" t="s">
         <v>189</v>
@@ -11593,7 +11593,7 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E41" t="s">
         <v>195</v>
@@ -11616,10 +11616,10 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F42" t="s">
         <v>189</v>
@@ -11639,7 +11639,7 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
         <v>193</v>
@@ -11662,7 +11662,7 @@
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E44" t="s">
         <v>195</v>
@@ -11685,10 +11685,10 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F45" t="s">
         <v>189</v>
@@ -11708,7 +11708,7 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E46" t="s">
         <v>197</v>
@@ -11731,10 +11731,10 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E47" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F47" t="s">
         <v>189</v>
@@ -11754,10 +11754,10 @@
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F48" t="s">
         <v>189</v>
@@ -11777,10 +11777,10 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="E49" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F49" t="s">
         <v>189</v>
@@ -11803,7 +11803,7 @@
         <v>76</v>
       </c>
       <c r="E50" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F50" t="s">
         <v>189</v>
@@ -11826,7 +11826,7 @@
         <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F51" t="s">
         <v>189</v>
@@ -11846,10 +11846,10 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E52" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F52" t="s">
         <v>189</v>
@@ -11869,10 +11869,10 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="E53" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F53" t="s">
         <v>189</v>
@@ -11892,10 +11892,10 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F54" t="s">
         <v>189</v>
@@ -11915,10 +11915,10 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F55" t="s">
         <v>189</v>
@@ -11938,10 +11938,10 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F56" t="s">
         <v>189</v>
@@ -11961,10 +11961,10 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="E57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F57" t="s">
         <v>189</v>
@@ -11978,22 +11978,22 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C58" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D58" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E58" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F58" t="s">
         <v>182</v>
       </c>
       <c r="G58" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H58"/>
       <c r="I58"/>
@@ -12004,19 +12004,19 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E59" t="s">
         <v>185</v>
       </c>
       <c r="F59" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G59" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="H59"/>
       <c r="I59"/>
@@ -12024,22 +12024,22 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D60" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E60" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F60" t="s">
         <v>182</v>
       </c>
       <c r="G60" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H60"/>
       <c r="I60"/>
@@ -12050,19 +12050,19 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E61" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F61" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G61" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="H61"/>
       <c r="I61"/>
@@ -12070,22 +12070,22 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="E62" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F62" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G62" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H62"/>
       <c r="I62"/>
@@ -12093,22 +12093,22 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="E63" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F63" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G63" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="H63"/>
       <c r="I63"/>
@@ -12116,22 +12116,22 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F64" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G64" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="H64"/>
       <c r="I64"/>
@@ -12154,7 +12154,7 @@
         <v>182</v>
       </c>
       <c r="G65" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="H65"/>
       <c r="I65"/>
@@ -12162,22 +12162,22 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E66" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F66" t="s">
         <v>182</v>
       </c>
       <c r="G66" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H66"/>
       <c r="I66"/>
@@ -12185,22 +12185,22 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D67" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F67" t="s">
         <v>182</v>
       </c>
       <c r="G67" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="H67"/>
       <c r="I67"/>
@@ -12208,13 +12208,13 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E68" t="s">
         <v>190</v>
@@ -12223,7 +12223,7 @@
         <v>182</v>
       </c>
       <c r="G68" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="H68"/>
       <c r="I68"/>
@@ -12234,19 +12234,19 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D69" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E69" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F69" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G69" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="H69"/>
       <c r="I69"/>
@@ -12254,13 +12254,13 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D70" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E70" t="s">
         <v>185</v>
@@ -12269,7 +12269,7 @@
         <v>182</v>
       </c>
       <c r="G70" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="H70"/>
       <c r="I70"/>
@@ -12283,16 +12283,16 @@
         <v>113</v>
       </c>
       <c r="D71" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E71" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F71" t="s">
         <v>182</v>
       </c>
       <c r="G71" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H71"/>
       <c r="I71"/>
@@ -12300,22 +12300,22 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D72" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="F72" t="s">
         <v>182</v>
       </c>
       <c r="G72" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="H72"/>
       <c r="I72"/>
@@ -12326,19 +12326,19 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D73" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E73" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F73" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="H73"/>
       <c r="I73"/>
@@ -12361,7 +12361,7 @@
         <v>182</v>
       </c>
       <c r="G74" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H74"/>
       <c r="I74"/>
@@ -12369,13 +12369,13 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E75" t="s">
         <v>185</v>
@@ -12384,7 +12384,7 @@
         <v>182</v>
       </c>
       <c r="G75" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H75"/>
       <c r="I75"/>
@@ -12395,19 +12395,19 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D76" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="E76" t="s">
         <v>185</v>
       </c>
       <c r="F76" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="H76"/>
       <c r="I76"/>
@@ -12424,13 +12424,13 @@
         <v>133</v>
       </c>
       <c r="E77" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F77" t="s">
         <v>182</v>
       </c>
       <c r="G77" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H77"/>
       <c r="I77"/>
@@ -12453,7 +12453,7 @@
         <v>182</v>
       </c>
       <c r="G78" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H78"/>
       <c r="I78"/>
@@ -12464,19 +12464,19 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E79" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F79" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G79" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="H79"/>
       <c r="I79"/>
@@ -12484,22 +12484,22 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C80" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D80" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="E80" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F80" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G80" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="H80"/>
       <c r="I80"/>
@@ -12507,13 +12507,13 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C81" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D81" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E81" t="s">
         <v>190</v>
@@ -12522,7 +12522,7 @@
         <v>182</v>
       </c>
       <c r="G81" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="H81"/>
       <c r="I81"/>
@@ -12530,16 +12530,16 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D82" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E82" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>182</v>
@@ -12562,13 +12562,13 @@
         <v>93</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F83" t="s">
         <v>182</v>
       </c>
       <c r="G83" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="H83"/>
       <c r="I83"/>
@@ -12576,22 +12576,22 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F84" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G84" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="H84"/>
       <c r="I84"/>
@@ -12605,10 +12605,10 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F85" t="s">
         <v>189</v>
@@ -12622,22 +12622,22 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D86" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="E86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F86" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G86" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="H86"/>
       <c r="I86"/>
@@ -12677,7 +12677,7 @@
         <v>93</v>
       </c>
       <c r="E88" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F88" t="s">
         <v>182</v>
@@ -12700,7 +12700,7 @@
         <v>93</v>
       </c>
       <c r="E89" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F89" t="s">
         <v>182</v>
@@ -12714,22 +12714,22 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F90" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G90" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="H90"/>
       <c r="I90"/>
@@ -12737,22 +12737,22 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C91" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D91" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E91" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F91" t="s">
         <v>182</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H91"/>
       <c r="I91"/>
@@ -12760,16 +12760,16 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D92" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E92" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F92" t="s">
         <v>182</v>
@@ -12783,22 +12783,22 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="E93" t="s">
         <v>185</v>
       </c>
       <c r="F93" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G93" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="H93"/>
       <c r="I93"/>
@@ -12812,10 +12812,10 @@
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="E94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F94" t="s">
         <v>189</v>
@@ -12829,13 +12829,13 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C95" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D95" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E95" t="s">
         <v>185</v>
@@ -12844,7 +12844,7 @@
         <v>182</v>
       </c>
       <c r="G95" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H95"/>
       <c r="I95"/>
@@ -12852,13 +12852,13 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D96" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E96" t="s">
         <v>185</v>
@@ -12867,7 +12867,7 @@
         <v>182</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H96"/>
       <c r="I96"/>
@@ -12881,10 +12881,10 @@
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F97" t="s">
         <v>189</v>

--- a/Version/BATCH/ETL/APP/CDM/BIN/tran_cdm_dim_cstm_dmns_h.xlsx
+++ b/Version/BATCH/ETL/APP/CDM/BIN/tran_cdm_dim_cstm_dmns_h.xlsx
@@ -589,19 +589,19 @@
     <t>0</t>
   </si>
   <si>
+    <t>s054_ecif_vwcust_f</t>
+  </si>
+  <si>
     <t>tran_cdm_dim_cstm_dmns_h.sql</t>
   </si>
   <si>
-    <t>s054_ecif_vwcust_f</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
+    <t>UNKN_</t>
+  </si>
+  <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t>UNKN_</t>
   </si>
   <si>
     <t>未添加企业微信</t>
@@ -11265,19 +11265,19 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F27" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G27" t="s">
         <v>149</v>
@@ -11297,7 +11297,7 @@
         <v>35</v>
       </c>
       <c r="E28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F28" t="s">
         <v>189</v>
@@ -11311,19 +11311,19 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F29" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G29" t="s">
         <v>149</v>
@@ -11340,10 +11340,10 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F30" t="s">
         <v>189</v>
@@ -11363,7 +11363,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
         <v>191</v>
@@ -11386,7 +11386,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s">
         <v>192</v>
@@ -11409,7 +11409,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
         <v>193</v>
@@ -11432,7 +11432,7 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
         <v>193</v>
@@ -11455,7 +11455,7 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E35" t="s">
         <v>194</v>
@@ -11478,7 +11478,7 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E36" t="s">
         <v>194</v>
@@ -11501,7 +11501,7 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
         <v>193</v>
@@ -11524,7 +11524,7 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="E38" t="s">
         <v>193</v>
@@ -11547,7 +11547,7 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="E39" t="s">
         <v>193</v>
@@ -11573,7 +11573,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F40" t="s">
         <v>189</v>
@@ -11642,7 +11642,7 @@
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F43" t="s">
         <v>189</v>
@@ -11662,10 +11662,10 @@
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E44" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F44" t="s">
         <v>189</v>
@@ -11685,10 +11685,10 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F45" t="s">
         <v>189</v>
@@ -11708,7 +11708,7 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
         <v>197</v>
@@ -11731,10 +11731,10 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F47" t="s">
         <v>189</v>
@@ -11754,10 +11754,10 @@
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F48" t="s">
         <v>189</v>
@@ -11777,7 +11777,7 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="E49" t="s">
         <v>195</v>
@@ -11800,10 +11800,10 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F50" t="s">
         <v>189</v>
@@ -11823,7 +11823,7 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E51" t="s">
         <v>194</v>
@@ -11849,7 +11849,7 @@
         <v>68</v>
       </c>
       <c r="E52" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F52" t="s">
         <v>189</v>
@@ -11869,10 +11869,10 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E53" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F53" t="s">
         <v>189</v>
@@ -11892,10 +11892,10 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F54" t="s">
         <v>189</v>
@@ -11915,10 +11915,10 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" t="s">
         <v>189</v>
@@ -11938,10 +11938,10 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E56" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F56" t="s">
         <v>189</v>
@@ -11961,10 +11961,10 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="E57" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F57" t="s">
         <v>189</v>
@@ -11978,22 +11978,22 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E58" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F58" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="H58"/>
       <c r="I58"/>
@@ -12001,22 +12001,22 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D59" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E59" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F59" t="s">
         <v>182</v>
       </c>
       <c r="G59" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="H59"/>
       <c r="I59"/>
@@ -12024,16 +12024,16 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E60" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F60" t="s">
         <v>182</v>
@@ -12050,19 +12050,19 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D61" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E61" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F61" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G61" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="H61"/>
       <c r="I61"/>
@@ -12070,13 +12070,13 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D62" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E62" t="s">
         <v>190</v>
@@ -12093,22 +12093,22 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D63" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F63" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G63" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="H63"/>
       <c r="I63"/>
@@ -12119,19 +12119,19 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D64" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F64" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G64" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H64"/>
       <c r="I64"/>
@@ -12142,19 +12142,19 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E65" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F65" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G65" t="s">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="H65"/>
       <c r="I65"/>
@@ -12162,22 +12162,22 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F66" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G66" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="H66"/>
       <c r="I66"/>
@@ -12188,19 +12188,19 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F67" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G67" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="H67"/>
       <c r="I67"/>
@@ -12208,13 +12208,13 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E68" t="s">
         <v>190</v>
@@ -12223,7 +12223,7 @@
         <v>182</v>
       </c>
       <c r="G68" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="H68"/>
       <c r="I68"/>
@@ -12246,7 +12246,7 @@
         <v>182</v>
       </c>
       <c r="G69" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="H69"/>
       <c r="I69"/>
@@ -12263,13 +12263,13 @@
         <v>93</v>
       </c>
       <c r="E70" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="F70" t="s">
         <v>182</v>
       </c>
       <c r="G70" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H70"/>
       <c r="I70"/>
@@ -12286,7 +12286,7 @@
         <v>142</v>
       </c>
       <c r="E71" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F71" t="s">
         <v>182</v>
@@ -12300,16 +12300,16 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C72" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D72" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F72" t="s">
         <v>182</v>
@@ -12323,13 +12323,13 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D73" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E73" t="s">
         <v>185</v>
@@ -12346,13 +12346,13 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D74" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E74" t="s">
         <v>185</v>
@@ -12369,22 +12369,22 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F75" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G75" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="H75"/>
       <c r="I75"/>
@@ -12392,13 +12392,13 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C76" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D76" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E76" t="s">
         <v>185</v>
@@ -12407,7 +12407,7 @@
         <v>182</v>
       </c>
       <c r="G76" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="H76"/>
       <c r="I76"/>
@@ -12415,22 +12415,22 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="E77" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F77" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G77" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="H77"/>
       <c r="I77"/>
@@ -12438,22 +12438,22 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="E78" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F78" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G78" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="H78"/>
       <c r="I78"/>
@@ -12461,22 +12461,22 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C79" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D79" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="E79" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F79" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G79" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="H79"/>
       <c r="I79"/>
@@ -12484,13 +12484,13 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D80" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E80" t="s">
         <v>185</v>
@@ -12499,7 +12499,7 @@
         <v>182</v>
       </c>
       <c r="G80" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="H80"/>
       <c r="I80"/>
@@ -12507,22 +12507,22 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="E81" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F81" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G81" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="H81"/>
       <c r="I81"/>
@@ -12530,22 +12530,22 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D82" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F82" t="s">
         <v>182</v>
       </c>
       <c r="G82" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H82"/>
       <c r="I82"/>
@@ -12568,7 +12568,7 @@
         <v>182</v>
       </c>
       <c r="G83" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="H83"/>
       <c r="I83"/>
@@ -12582,7 +12582,7 @@
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E84" t="s">
         <v>185</v>
@@ -12602,19 +12602,19 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="E85" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F85" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G85" t="s">
-        <v>149</v>
+        <v>37</v>
       </c>
       <c r="H85"/>
       <c r="I85"/>
@@ -12622,22 +12622,22 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="E86" t="s">
         <v>185</v>
       </c>
       <c r="F86" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G86" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="H86"/>
       <c r="I86"/>
@@ -12645,13 +12645,13 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E87" t="s">
         <v>185</v>
@@ -12660,7 +12660,7 @@
         <v>182</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="H87"/>
       <c r="I87"/>
@@ -12668,22 +12668,22 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D88" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E88" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F88" t="s">
         <v>182</v>
       </c>
       <c r="G88" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="H88"/>
       <c r="I88"/>
@@ -12691,22 +12691,22 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C89" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D89" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E89" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F89" t="s">
         <v>182</v>
       </c>
       <c r="G89" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H89"/>
       <c r="I89"/>
@@ -12717,19 +12717,19 @@
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D90" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F90" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G90" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="H90"/>
       <c r="I90"/>
@@ -12737,22 +12737,22 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E91" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F91" t="s">
         <v>182</v>
       </c>
       <c r="G91" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="H91"/>
       <c r="I91"/>
@@ -12766,10 +12766,10 @@
         <v>113</v>
       </c>
       <c r="D92" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E92" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F92" t="s">
         <v>182</v>
@@ -12783,22 +12783,22 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C93" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D93" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="E93" t="s">
         <v>185</v>
       </c>
       <c r="F93" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G93" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H93"/>
       <c r="I93"/>
@@ -12806,22 +12806,22 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C94" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D94" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="E94" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F94" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G94" t="s">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="H94"/>
       <c r="I94"/>
@@ -12835,16 +12835,16 @@
         <v>113</v>
       </c>
       <c r="D95" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E95" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F95" t="s">
         <v>182</v>
       </c>
       <c r="G95" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="H95"/>
       <c r="I95"/>
@@ -12852,13 +12852,13 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C96" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D96" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E96" t="s">
         <v>185</v>
@@ -12867,7 +12867,7 @@
         <v>182</v>
       </c>
       <c r="G96" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H96"/>
       <c r="I96"/>
@@ -12878,19 +12878,19 @@
         <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D97" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E97" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F97" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G97" t="s">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="H97"/>
       <c r="I97"/>

--- a/Version/BATCH/ETL/APP/CDM/BIN/tran_cdm_dim_cstm_dmns_h.xlsx
+++ b/Version/BATCH/ETL/APP/CDM/BIN/tran_cdm_dim_cstm_dmns_h.xlsx
@@ -589,31 +589,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>tran_cdm_dim_cstm_dmns_h.sql</t>
+  </si>
+  <si>
     <t>s054_ecif_vwcust_f</t>
   </si>
   <si>
-    <t>tran_cdm_dim_cstm_dmns_h.sql</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>未添加企业微信</t>
+  </si>
+  <si>
     <t>UNKN_</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>未添加企业微信</t>
-  </si>
-  <si>
     <t>365</t>
   </si>
   <si>
+    <t>1+0</t>
+  </si>
+  <si>
     <t>18</t>
-  </si>
-  <si>
-    <t>1+0</t>
   </si>
   <si>
     <t>来源系统名</t>
@@ -11265,19 +11265,19 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F27" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G27" t="s">
         <v>149</v>
@@ -11288,19 +11288,19 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G28" t="s">
         <v>149</v>
@@ -11363,7 +11363,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
         <v>191</v>
@@ -11386,7 +11386,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
         <v>192</v>
@@ -11409,7 +11409,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
         <v>193</v>
@@ -11432,7 +11432,7 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E34" t="s">
         <v>193</v>
@@ -11455,10 +11455,10 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F35" t="s">
         <v>189</v>
@@ -11478,10 +11478,10 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F36" t="s">
         <v>189</v>
@@ -11501,10 +11501,10 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F37" t="s">
         <v>189</v>
@@ -11524,10 +11524,10 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F38" t="s">
         <v>189</v>
@@ -11547,10 +11547,10 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F39" t="s">
         <v>189</v>
@@ -11570,7 +11570,7 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="E40" t="s">
         <v>195</v>
@@ -11593,10 +11593,10 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F41" t="s">
         <v>189</v>
@@ -11616,7 +11616,7 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E42" t="s">
         <v>196</v>
@@ -11642,7 +11642,7 @@
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F43" t="s">
         <v>189</v>
@@ -11685,10 +11685,10 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F45" t="s">
         <v>189</v>
@@ -11708,10 +11708,10 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F46" t="s">
         <v>189</v>
@@ -11731,10 +11731,10 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F47" t="s">
         <v>189</v>
@@ -11754,10 +11754,10 @@
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E48" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F48" t="s">
         <v>189</v>
@@ -11777,10 +11777,10 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="E49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F49" t="s">
         <v>189</v>
@@ -11800,10 +11800,10 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F50" t="s">
         <v>189</v>
@@ -11823,7 +11823,7 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="E51" t="s">
         <v>194</v>
@@ -11846,7 +11846,7 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="E52" t="s">
         <v>194</v>
@@ -11869,10 +11869,10 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E53" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F53" t="s">
         <v>189</v>
@@ -11892,10 +11892,10 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E54" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F54" t="s">
         <v>189</v>
@@ -11915,10 +11915,10 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="E55" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F55" t="s">
         <v>189</v>
@@ -11938,10 +11938,10 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E56" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F56" t="s">
         <v>189</v>
@@ -11964,7 +11964,7 @@
         <v>54</v>
       </c>
       <c r="E57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F57" t="s">
         <v>189</v>
@@ -11981,19 +11981,19 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D58" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F58" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G58" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H58"/>
       <c r="I58"/>
@@ -12007,16 +12007,16 @@
         <v>113</v>
       </c>
       <c r="D59" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E59" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F59" t="s">
         <v>182</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="H59"/>
       <c r="I59"/>
@@ -12024,22 +12024,22 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D60" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E60" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="F60" t="s">
         <v>182</v>
       </c>
       <c r="G60" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="H60"/>
       <c r="I60"/>
@@ -12050,19 +12050,19 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F61" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G61" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="H61"/>
       <c r="I61"/>
@@ -12079,13 +12079,13 @@
         <v>93</v>
       </c>
       <c r="E62" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F62" t="s">
         <v>182</v>
       </c>
       <c r="G62" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H62"/>
       <c r="I62"/>
@@ -12108,7 +12108,7 @@
         <v>182</v>
       </c>
       <c r="G63" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="H63"/>
       <c r="I63"/>
@@ -12116,13 +12116,13 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D64" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
         <v>185</v>
@@ -12131,7 +12131,7 @@
         <v>182</v>
       </c>
       <c r="G64" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H64"/>
       <c r="I64"/>
@@ -12145,10 +12145,10 @@
         <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F65" t="s">
         <v>189</v>
@@ -12162,22 +12162,22 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D66" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="E66" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F66" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G66" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="H66"/>
       <c r="I66"/>
@@ -12208,22 +12208,22 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="E68" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F68" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G68" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="H68"/>
       <c r="I68"/>
@@ -12231,13 +12231,13 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D69" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E69" t="s">
         <v>185</v>
@@ -12246,7 +12246,7 @@
         <v>182</v>
       </c>
       <c r="G69" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="H69"/>
       <c r="I69"/>
@@ -12254,22 +12254,22 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C70" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D70" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E70" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F70" t="s">
         <v>182</v>
       </c>
       <c r="G70" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H70"/>
       <c r="I70"/>
@@ -12277,22 +12277,22 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D71" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E71" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F71" t="s">
         <v>182</v>
       </c>
       <c r="G71" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H71"/>
       <c r="I71"/>
@@ -12300,22 +12300,22 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D72" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F72" t="s">
         <v>182</v>
       </c>
       <c r="G72" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="H72"/>
       <c r="I72"/>
@@ -12323,22 +12323,22 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="E73" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F73" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G73" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="H73"/>
       <c r="I73"/>
@@ -12355,13 +12355,13 @@
         <v>93</v>
       </c>
       <c r="E74" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F74" t="s">
         <v>182</v>
       </c>
       <c r="G74" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="H74"/>
       <c r="I74"/>
@@ -12372,19 +12372,19 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E75" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F75" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G75" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="H75"/>
       <c r="I75"/>
@@ -12392,22 +12392,22 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D76" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E76" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F76" t="s">
         <v>182</v>
       </c>
       <c r="G76" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H76"/>
       <c r="I76"/>
@@ -12418,19 +12418,19 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D77" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="E77" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F77" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="H77"/>
       <c r="I77"/>
@@ -12438,22 +12438,22 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D78" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="E78" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F78" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G78" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="H78"/>
       <c r="I78"/>
@@ -12476,7 +12476,7 @@
         <v>182</v>
       </c>
       <c r="G79" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="H79"/>
       <c r="I79"/>
@@ -12487,19 +12487,19 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="E80" t="s">
         <v>185</v>
       </c>
       <c r="F80" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="H80"/>
       <c r="I80"/>
@@ -12507,22 +12507,22 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C81" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="E81" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F81" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G81" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H81"/>
       <c r="I81"/>
@@ -12536,16 +12536,16 @@
         <v>113</v>
       </c>
       <c r="D82" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E82" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F82" t="s">
         <v>182</v>
       </c>
       <c r="G82" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H82"/>
       <c r="I82"/>
@@ -12553,13 +12553,13 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D83" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E83" t="s">
         <v>185</v>
@@ -12568,7 +12568,7 @@
         <v>182</v>
       </c>
       <c r="G83" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H83"/>
       <c r="I83"/>
@@ -12579,19 +12579,19 @@
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D84" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="E84" t="s">
         <v>185</v>
       </c>
       <c r="F84" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G84" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="H84"/>
       <c r="I84"/>
@@ -12608,13 +12608,13 @@
         <v>93</v>
       </c>
       <c r="E85" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F85" t="s">
         <v>182</v>
       </c>
       <c r="G85" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="H85"/>
       <c r="I85"/>
@@ -12625,19 +12625,19 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D86" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E86" t="s">
         <v>185</v>
       </c>
       <c r="F86" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G86" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="H86"/>
       <c r="I86"/>
@@ -12645,22 +12645,22 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D87" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E87" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>182</v>
       </c>
       <c r="G87" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H87"/>
       <c r="I87"/>
@@ -12668,13 +12668,13 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D88" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E88" t="s">
         <v>185</v>
@@ -12683,7 +12683,7 @@
         <v>182</v>
       </c>
       <c r="G88" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H88"/>
       <c r="I88"/>
@@ -12691,22 +12691,22 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D89" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E89" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F89" t="s">
         <v>182</v>
       </c>
       <c r="G89" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="H89"/>
       <c r="I89"/>
@@ -12729,7 +12729,7 @@
         <v>182</v>
       </c>
       <c r="G90" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H90"/>
       <c r="I90"/>
@@ -12740,19 +12740,19 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="E91" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F91" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G91" t="s">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="H91"/>
       <c r="I91"/>
@@ -12766,10 +12766,10 @@
         <v>113</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E92" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="F92" t="s">
         <v>182</v>
@@ -12789,10 +12789,10 @@
         <v>113</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E93" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F93" t="s">
         <v>182</v>
@@ -12806,22 +12806,22 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="E94" t="s">
         <v>185</v>
       </c>
       <c r="F94" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G94" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="H94"/>
       <c r="I94"/>
@@ -12829,22 +12829,22 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="E95" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F95" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G95" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="H95"/>
       <c r="I95"/>
@@ -12867,7 +12867,7 @@
         <v>182</v>
       </c>
       <c r="G96" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="H96"/>
       <c r="I96"/>
@@ -12878,19 +12878,19 @@
         <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E97" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F97" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G97" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="H97"/>
       <c r="I97"/>
